--- a/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna</t>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,18; 69,89</t>
+          <t>44,54; 68,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,12; 72,35</t>
+          <t>52,0; 72,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,83; 68,8</t>
+          <t>51,63; 66,77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 30,7</t>
+          <t>16,3; 31,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 32,55</t>
+          <t>16,25; 33,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 30,29</t>
+          <t>17,65; 29,84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,62; 70,07</t>
+          <t>49,48; 69,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,79; 70,6</t>
+          <t>49,82; 70,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,16; 67,31</t>
+          <t>53,23; 67,29</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,37; 50,38</t>
+          <t>29,56; 50,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,47; 68,3</t>
+          <t>29,06; 67,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,01; 56,79</t>
+          <t>33,13; 55,69</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,82; 71,0</t>
+          <t>46,6; 70,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,65; 69,08</t>
+          <t>45,35; 69,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,32; 66,36</t>
+          <t>49,49; 66,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,73; 87,47</t>
+          <t>68,35; 86,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,92; 90,35</t>
+          <t>71,5; 90,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,11; 87,14</t>
+          <t>74,02; 87,1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,94; 69,6</t>
+          <t>54,13; 69,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,92; 71,83</t>
+          <t>54,45; 71,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,61; 69,28</t>
+          <t>57,09; 68,29</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,6; 50,72</t>
+          <t>35,2; 50,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,59; 47,82</t>
+          <t>33,42; 47,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,97; 46,78</t>
+          <t>36,73; 46,51</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45,94; 53,39</t>
+          <t>46,03; 53,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,13; 54,86</t>
+          <t>47,06; 54,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,7; 52,83</t>
+          <t>47,79; 52,99</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>40665</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>86958</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>31799; 48979</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38794; 53824</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75376; 97487</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>22610</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51039</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>15832; 30184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20102; 41852</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38958; 65884</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>33608</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38608</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72215</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>27710; 38986</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31859; 45233</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>63855; 80714</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26658</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32557</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59215</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20037; 34395</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>21466; 49494</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>46931; 78883</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23618</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43825</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15939; 23949</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18468; 28376</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37081; 49852</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>33763</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45135</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>78898</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>29246; 37213</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>38454; 48799</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>71483; 84117</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>75331</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>99036</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>174367</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>65943; 85103</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>84163; 110728</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>157806; 188739</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>54229</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>62407</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>116637</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>44867; 64113</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>51424; 73708</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>103332; 130859</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>307072</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>376082</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>683154</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>284750; 328568</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>347770; 404953</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>648831; 719338</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 68,6</t>
+          <t>45,45; 69,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,0; 72,14</t>
+          <t>50,55; 71,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,63; 66,77</t>
+          <t>50,68; 67,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 31,08</t>
+          <t>16,56; 31,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 33,84</t>
+          <t>15,06; 32,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 29,84</t>
+          <t>17,88; 29,24</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 69,62</t>
+          <t>48,73; 69,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,82; 70,73</t>
+          <t>49,51; 70,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,23; 67,29</t>
+          <t>53,42; 67,5</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 50,74</t>
+          <t>29,49; 49,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,06; 67,0</t>
+          <t>30,03; 68,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 55,69</t>
+          <t>32,61; 56,99</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,6; 70,03</t>
+          <t>46,67; 71,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,35; 69,69</t>
+          <t>45,15; 69,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,49; 66,54</t>
+          <t>49,71; 66,52</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,35; 86,97</t>
+          <t>67,66; 86,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,5; 90,73</t>
+          <t>70,16; 90,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,02; 87,1</t>
+          <t>73,49; 86,84</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54,13; 69,86</t>
+          <t>53,93; 69,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,45; 71,63</t>
+          <t>54,05; 71,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,09; 68,29</t>
+          <t>56,6; 68,4</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,2; 50,3</t>
+          <t>35,76; 50,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,42; 47,9</t>
+          <t>33,62; 47,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,73; 46,51</t>
+          <t>36,8; 47,06</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,03; 53,12</t>
+          <t>46,3; 53,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,06; 54,79</t>
+          <t>47,2; 54,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,79; 52,99</t>
+          <t>47,61; 52,98</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31799; 48979</t>
+          <t>32450; 49626</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38794; 53824</t>
+          <t>37717; 53220</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75376; 97487</t>
+          <t>73995; 98493</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15832; 30184</t>
+          <t>16076; 30184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20102; 41852</t>
+          <t>18627; 40179</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38958; 65884</t>
+          <t>39466; 64552</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27710; 38986</t>
+          <t>27287; 39026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31859; 45233</t>
+          <t>31666; 44925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63855; 80714</t>
+          <t>64076; 80962</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20037; 34395</t>
+          <t>19990; 33517</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21466; 49494</t>
+          <t>22182; 50791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46931; 78883</t>
+          <t>46191; 80724</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15939; 23949</t>
+          <t>15961; 24499</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18468; 28376</t>
+          <t>18385; 28195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37081; 49852</t>
+          <t>37245; 49838</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29246; 37213</t>
+          <t>28951; 37150</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38454; 48799</t>
+          <t>37731; 48760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71483; 84117</t>
+          <t>70971; 83859</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65943; 85103</t>
+          <t>65693; 84725</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84163; 110728</t>
+          <t>83557; 110594</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>157806; 188739</t>
+          <t>156429; 189046</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44867; 64113</t>
+          <t>45587; 64261</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51424; 73708</t>
+          <t>51726; 73541</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103332; 130859</t>
+          <t>103534; 132392</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>284750; 328568</t>
+          <t>286377; 329456</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>347770; 404953</t>
+          <t>348861; 404445</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>648831; 719338</t>
+          <t>646341; 719224</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,45; 69,5</t>
+          <t>49,3; 70,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,55; 71,33</t>
+          <t>39,93; 60,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,68; 67,46</t>
+          <t>47,51; 62,45</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 31,08</t>
+          <t>16,13; 33,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 32,49</t>
+          <t>16,56; 32,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 29,24</t>
+          <t>18,72; 31,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,73; 69,69</t>
+          <t>50,95; 70,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,51; 70,25</t>
+          <t>50,16; 70,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,42; 67,5</t>
+          <t>53,25; 67,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,49; 49,44</t>
+          <t>28,62; 64,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 68,76</t>
+          <t>29,21; 50,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,61; 56,99</t>
+          <t>32,45; 53,15</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,67; 71,63</t>
+          <t>43,56; 67,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,15; 69,24</t>
+          <t>46,74; 71,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,71; 66,52</t>
+          <t>48,8; 65,92</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,66; 86,82</t>
+          <t>72,86; 91,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,16; 90,66</t>
+          <t>68,47; 87,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,49; 86,84</t>
+          <t>73,86; 87,66</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,89%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,93; 69,55</t>
+          <t>57,1; 72,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,05; 71,54</t>
+          <t>56,04; 71,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,6; 68,4</t>
+          <t>58,5; 69,72</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,76; 50,41</t>
+          <t>33,97; 48,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,62; 47,8</t>
+          <t>35,61; 50,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,8; 47,06</t>
+          <t>37,05; 47,11</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,3; 53,26</t>
+          <t>46,79; 54,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,73</t>
+          <t>45,94; 52,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,61; 52,98</t>
+          <t>47,36; 52,2</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>63044</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32450; 49626</t>
+          <t>29710; 42317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37717; 53220</t>
+          <t>21931; 33031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73995; 98493</t>
+          <t>54729; 71929</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>49652</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16076; 30184</t>
+          <t>18133; 37738</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18627; 40179</t>
+          <t>15724; 30425</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39466; 64552</t>
+          <t>38819; 65042</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72215</t>
+          <t>67178</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27287; 39026</t>
+          <t>28876; 40072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31666; 44925</t>
+          <t>27354; 38418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64076; 80962</t>
+          <t>59222; 75119</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>56377</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19990; 33517</t>
+          <t>19572; 44165</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22182; 50791</t>
+          <t>19984; 34749</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46191; 80724</t>
+          <t>44391; 72715</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>43536</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15961; 24499</t>
+          <t>17241; 26861</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18385; 28195</t>
+          <t>16531; 25340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37245; 49838</t>
+          <t>36572; 49407</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78898</t>
+          <t>73862</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28951; 37150</t>
+          <t>34396; 43018</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37731; 48760</t>
+          <t>29290; 37562</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70971; 83859</t>
+          <t>66463; 78886</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>75331</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>99036</t>
+          <t>75445</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174367</t>
+          <t>166072</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65693; 84725</t>
+          <t>80036; 101050</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83557; 110594</t>
+          <t>67124; 85047</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156429; 189046</t>
+          <t>152057; 181223</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>64306</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>62407</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116637</t>
+          <t>122526</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45587; 64261</t>
+          <t>53207; 75718</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51726; 73541</t>
+          <t>48430; 69242</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103534; 132392</t>
+          <t>108436; 137871</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>448</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>343094</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>286377; 329456</t>
+          <t>318777; 369021</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>348861; 404445</t>
+          <t>278773; 321070</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>646341; 719224</t>
+          <t>610007; 672454</t>
         </is>
       </c>
     </row>
